--- a/artfynd/A 63676-2025 artfynd.xlsx
+++ b/artfynd/A 63676-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124862912</v>
+        <v>128676522</v>
       </c>
       <c r="B2" t="n">
-        <v>78947</v>
+        <v>90932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,40 +686,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blankstjärn, Dlr</t>
+          <t>Blanktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>451208</v>
+        <v>451203</v>
       </c>
       <c r="R2" t="n">
-        <v>6709512</v>
+        <v>6709660</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -743,12 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,22 +768,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124863021</v>
+        <v>128676568</v>
       </c>
       <c r="B3" t="n">
-        <v>78947</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,40 +791,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blankstjärn, Dlr</t>
+          <t>Blanktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>451148</v>
+        <v>451227</v>
       </c>
       <c r="R3" t="n">
-        <v>6709550</v>
+        <v>6709725</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -844,12 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -865,22 +873,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124862901</v>
+        <v>128676575</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,40 +896,44 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blankstjärn, Dlr</t>
+          <t>Blanktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451194</v>
+        <v>451285</v>
       </c>
       <c r="R4" t="n">
-        <v>6709513</v>
+        <v>6709660</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -945,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,22 +978,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124863049</v>
+        <v>128676484</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,40 +1001,44 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Blankstjärn, Dlr</t>
+          <t>Blanktjärn, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451155</v>
+        <v>451251</v>
       </c>
       <c r="R5" t="n">
-        <v>6709561</v>
+        <v>6709574</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1046,12 +1062,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1067,26 +1083,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124862987</v>
+        <v>124862901</v>
       </c>
       <c r="B6" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1117,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>451183</v>
+        <v>451194</v>
       </c>
       <c r="R6" t="n">
-        <v>6709547</v>
+        <v>6709513</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1180,14 +1196,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124863010</v>
+        <v>124862912</v>
       </c>
       <c r="B7" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1218,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451163</v>
+        <v>451208</v>
       </c>
       <c r="R7" t="n">
-        <v>6709539</v>
+        <v>6709512</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1281,14 +1297,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124863208</v>
+        <v>124862972</v>
       </c>
       <c r="B8" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1319,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451244</v>
+        <v>451167</v>
       </c>
       <c r="R8" t="n">
-        <v>6709610</v>
+        <v>6709559</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1382,14 +1398,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124863201</v>
+        <v>124862987</v>
       </c>
       <c r="B9" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1420,10 +1436,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>451250</v>
+        <v>451183</v>
       </c>
       <c r="R9" t="n">
-        <v>6709591</v>
+        <v>6709547</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1483,14 +1499,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124863157</v>
+        <v>124863010</v>
       </c>
       <c r="B10" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1521,10 +1537,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451181</v>
+        <v>451163</v>
       </c>
       <c r="R10" t="n">
-        <v>6709688</v>
+        <v>6709539</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1584,14 +1600,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124862972</v>
+        <v>124863021</v>
       </c>
       <c r="B11" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1622,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>451167</v>
+        <v>451148</v>
       </c>
       <c r="R11" t="n">
-        <v>6709559</v>
+        <v>6709550</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1685,14 +1701,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124863193</v>
+        <v>124863049</v>
       </c>
       <c r="B12" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1723,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451220</v>
+        <v>451155</v>
       </c>
       <c r="R12" t="n">
-        <v>6709614</v>
+        <v>6709561</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1789,11 +1805,11 @@
         <v>124863141</v>
       </c>
       <c r="B13" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1887,14 +1903,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124863173</v>
+        <v>124863157</v>
       </c>
       <c r="B14" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1925,10 +1941,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>451230</v>
+        <v>451181</v>
       </c>
       <c r="R14" t="n">
-        <v>6709603</v>
+        <v>6709688</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -1988,32 +2004,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124862955</v>
+        <v>124863173</v>
       </c>
       <c r="B15" t="n">
-        <v>78683</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2026,10 +2042,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>451085</v>
+        <v>451230</v>
       </c>
       <c r="R15" t="n">
-        <v>6709545</v>
+        <v>6709603</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2092,11 +2108,11 @@
         <v>124863180</v>
       </c>
       <c r="B16" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2190,14 +2206,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124863263</v>
+        <v>124863186</v>
       </c>
       <c r="B17" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2228,10 +2244,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451367</v>
+        <v>451213</v>
       </c>
       <c r="R17" t="n">
-        <v>6709547</v>
+        <v>6709596</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2291,14 +2307,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124863258</v>
+        <v>124863193</v>
       </c>
       <c r="B18" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2329,10 +2345,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451347</v>
+        <v>451220</v>
       </c>
       <c r="R18" t="n">
-        <v>6709539</v>
+        <v>6709614</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2392,14 +2408,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124863186</v>
+        <v>124863201</v>
       </c>
       <c r="B19" t="n">
-        <v>78947</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2430,10 +2446,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451213</v>
+        <v>451250</v>
       </c>
       <c r="R19" t="n">
-        <v>6709596</v>
+        <v>6709591</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2493,52 +2509,51 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128678518</v>
+        <v>124863208</v>
       </c>
       <c r="B20" t="n">
-        <v>57722</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Blanktjärn, Dlr</t>
+          <t>Blankstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451065</v>
+        <v>451244</v>
       </c>
       <c r="R20" t="n">
-        <v>6709628</v>
+        <v>6709610</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2562,27 +2577,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Föfohål</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2591,78 +2591,70 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128676133</v>
+        <v>124863258</v>
       </c>
       <c r="B21" t="n">
-        <v>56915</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Blanktjärn, Dlr</t>
+          <t>Blankstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451051</v>
+        <v>451347</v>
       </c>
       <c r="R21" t="n">
-        <v>6709472</v>
+        <v>6709539</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2686,17 +2678,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Sandbadade.</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2705,73 +2692,70 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128676568</v>
+        <v>124863263</v>
       </c>
       <c r="B22" t="n">
-        <v>92826</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Blanktjärn, Dlr</t>
+          <t>Blankstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>451227</v>
+        <v>451367</v>
       </c>
       <c r="R22" t="n">
-        <v>6709725</v>
+        <v>6709547</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2795,12 +2779,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2816,54 +2800,49 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128675896</v>
+        <v>128676602</v>
       </c>
       <c r="B23" t="n">
-        <v>57725</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2871,10 +2850,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451053</v>
+        <v>451152</v>
       </c>
       <c r="R23" t="n">
-        <v>6709479</v>
+        <v>6709741</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2901,17 +2880,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Flera meter längs stammen med ringhack, äldre tall.</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2920,6 +2894,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2938,42 +2913,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128676160</v>
+        <v>128676614</v>
       </c>
       <c r="B24" t="n">
-        <v>57722</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2981,10 +2951,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451069</v>
+        <v>451194</v>
       </c>
       <c r="R24" t="n">
-        <v>6709491</v>
+        <v>6709719</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3011,12 +2981,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3025,6 +2995,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3043,39 +3014,35 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128676522</v>
+        <v>128676628</v>
       </c>
       <c r="B25" t="n">
-        <v>90562</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3085,10 +3052,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451203</v>
+        <v>451214</v>
       </c>
       <c r="R25" t="n">
-        <v>6709660</v>
+        <v>6709680</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3148,39 +3115,35 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128676484</v>
+        <v>128676637</v>
       </c>
       <c r="B26" t="n">
-        <v>91553</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3190,10 +3153,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451251</v>
+        <v>451224</v>
       </c>
       <c r="R26" t="n">
-        <v>6709574</v>
+        <v>6709641</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3220,12 +3183,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3253,10 +3216,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128678551</v>
+        <v>124862955</v>
       </c>
       <c r="B27" t="n">
-        <v>57725</v>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3264,41 +3227,40 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Blanktjärn, Dlr</t>
+          <t>Blankstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>451311</v>
+        <v>451085</v>
       </c>
       <c r="R27" t="n">
-        <v>6709668</v>
+        <v>6709545</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3322,61 +3284,47 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>hack</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128676237</v>
+        <v>128676160</v>
       </c>
       <c r="B28" t="n">
-        <v>57722</v>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3402,7 +3350,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3412,10 +3360,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>451256</v>
+        <v>451069</v>
       </c>
       <c r="R28" t="n">
-        <v>6709506</v>
+        <v>6709491</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3474,37 +3422,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128676557</v>
+        <v>128676237</v>
       </c>
       <c r="B29" t="n">
-        <v>78797</v>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3512,13 +3465,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>451186</v>
+        <v>451256</v>
       </c>
       <c r="R29" t="n">
-        <v>6709680</v>
+        <v>6709506</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3542,12 +3495,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3556,7 +3509,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3575,37 +3527,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128676602</v>
+        <v>128678518</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3613,13 +3566,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>451152</v>
+        <v>451065</v>
       </c>
       <c r="R30" t="n">
-        <v>6709741</v>
+        <v>6709628</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3643,12 +3596,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Föfohål</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3657,7 +3625,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3676,41 +3643,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128676575</v>
+        <v>128675896</v>
       </c>
       <c r="B31" t="n">
-        <v>92826</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3718,10 +3686,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>451285</v>
+        <v>451053</v>
       </c>
       <c r="R31" t="n">
-        <v>6709660</v>
+        <v>6709479</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3748,12 +3716,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Flera meter längs stammen med ringhack, äldre tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3762,7 +3735,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3781,10 +3753,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128676614</v>
+        <v>128676197</v>
       </c>
       <c r="B32" t="n">
-        <v>79039</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3792,26 +3764,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3819,10 +3796,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>451194</v>
+        <v>451346</v>
       </c>
       <c r="R32" t="n">
-        <v>6709719</v>
+        <v>6709525</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3849,12 +3826,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack i äldre tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3863,7 +3845,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3882,10 +3863,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128676628</v>
+        <v>128678551</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3893,26 +3874,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3920,13 +3902,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>451214</v>
+        <v>451311</v>
       </c>
       <c r="R33" t="n">
-        <v>6709680</v>
+        <v>6709668</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3950,21 +3932,35 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>hack</t>
         </is>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3983,10 +3979,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128678480</v>
+        <v>128676133</v>
       </c>
       <c r="B34" t="n">
-        <v>97540</v>
+        <v>57141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3994,35 +3990,35 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4030,13 +4026,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>451104</v>
+        <v>451051</v>
       </c>
       <c r="R34" t="n">
-        <v>6709597</v>
+        <v>6709472</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4063,19 +4059,14 @@
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:00</t>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Sandbadade.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4084,7 +4075,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4106,7 +4096,7 @@
         <v>128676593</v>
       </c>
       <c r="B35" t="n">
-        <v>8450</v>
+        <v>8455</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4210,37 +4200,46 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128676541</v>
+        <v>128678480</v>
       </c>
       <c r="B36" t="n">
-        <v>78797</v>
+        <v>97983</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4248,13 +4247,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451164</v>
+        <v>451104</v>
       </c>
       <c r="R36" t="n">
-        <v>6709723</v>
+        <v>6709597</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4278,12 +4277,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4311,10 +4320,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128676637</v>
+        <v>128676541</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>79085</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4322,21 +4331,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4349,10 +4358,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>451224</v>
+        <v>451164</v>
       </c>
       <c r="R37" t="n">
-        <v>6709641</v>
+        <v>6709723</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4409,6 +4418,107 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128676557</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Blanktjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>451186</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6709680</v>
+      </c>
+      <c r="S38" t="n">
+        <v>50</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>FREDRIK Månsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63676-2025 artfynd.xlsx
+++ b/artfynd/A 63676-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676522</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676568</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676575</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676484</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124862901</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124862912</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1395,6 +1430,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124862972</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124862987</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1597,6 +1642,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124863010</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1698,6 +1748,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124863021</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1799,6 +1854,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124863049</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1900,6 +1960,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124863141</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2001,6 +2066,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124863157</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2102,6 +2172,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124863173</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2203,6 +2278,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124863180</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2304,6 +2384,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124863186</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2405,6 +2490,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124863193</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2506,6 +2596,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124863201</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2607,6 +2702,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124863208</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2708,6 +2808,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124863258</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2809,6 +2914,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124863263</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2910,6 +3020,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676602</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3011,6 +3126,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676614</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3112,6 +3232,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676628</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3213,6 +3338,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676637</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3314,6 +3444,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124862955</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3419,6 +3554,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676160</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3524,6 +3664,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676237</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3640,6 +3785,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128678518</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3750,6 +3900,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675896</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3860,6 +4015,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676197</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3976,6 +4136,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128678551</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4090,6 +4255,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676133</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4197,6 +4367,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676593</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4317,6 +4492,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128678480</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4418,6 +4598,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676541</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4519,8 +4704,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676557</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>